--- a/product_selector_out/STM32F1 series.xlsx
+++ b/product_selector_out/STM32F1 series.xlsx
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AL12" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM12" s="4" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM13" s="4" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AL14" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM14" s="4" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM15" s="4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AL16" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM16" s="4" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AL17" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM17" s="4" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AL18" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM18" s="4" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM19" s="4" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AL20" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM20" s="4" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AL21" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM21" s="4" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="AL35" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM35" s="4" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="AL36" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM36" s="4" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AL38" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM38" s="4" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="AL40" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM40" s="4" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="AL43" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM43" s="4" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="AL44" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM44" s="4" t="inlineStr">
@@ -23003,74 +23003,74 @@
       </c>
       <c r="U79" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V79" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA79" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V79" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA79" s="4" t="inlineStr">
+      <c r="AB79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD79" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AE79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG79" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH79" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD79" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AE79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH79" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI79" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -23088,7 +23088,7 @@
       </c>
       <c r="AL79" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM79" s="4" t="inlineStr">
@@ -23330,74 +23330,74 @@
       </c>
       <c r="U80" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V80" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA80" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V80" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA80" s="4" t="inlineStr">
+      <c r="AB80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD80" s="4" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AE80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG80" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH80" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD80" s="4" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AE80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG80" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH80" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI80" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -23415,7 +23415,7 @@
       </c>
       <c r="AL80" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM80" s="4" t="inlineStr">
@@ -23657,74 +23657,74 @@
       </c>
       <c r="U81" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V81" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA81" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V81" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA81" s="4" t="inlineStr">
+      <c r="AB81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD81" s="4" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AE81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG81" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH81" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD81" s="4" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AE81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG81" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH81" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI81" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AL81" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM81" s="4" t="inlineStr">
@@ -23984,74 +23984,74 @@
       </c>
       <c r="U82" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V82" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA82" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V82" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA82" s="4" t="inlineStr">
+      <c r="AB82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD82" s="4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AE82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH82" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD82" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AE82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG82" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH82" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI82" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="AL82" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM82" s="4" t="inlineStr">
@@ -24311,74 +24311,74 @@
       </c>
       <c r="U83" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V83" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA83" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V83" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA83" s="4" t="inlineStr">
+      <c r="AB83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD83" s="4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AE83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG83" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH83" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD83" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AE83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH83" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI83" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -24396,7 +24396,7 @@
       </c>
       <c r="AL83" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM83" s="4" t="inlineStr">
@@ -24965,74 +24965,74 @@
       </c>
       <c r="U85" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V85" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA85" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V85" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA85" s="4" t="inlineStr">
+      <c r="AB85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD85" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AE85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG85" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH85" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD85" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AE85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG85" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH85" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI85" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="AL85" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM85" s="4" t="inlineStr">
@@ -32829,14 +32829,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="8" t="inlineStr">
@@ -32859,9 +32859,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="8" t="inlineStr">
@@ -32914,9 +32914,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM12" s="6" t="inlineStr">
@@ -33156,14 +33156,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="8" t="inlineStr">
@@ -33186,9 +33186,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr">
@@ -33241,9 +33241,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM13" s="6" t="inlineStr">
@@ -33483,14 +33483,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
@@ -33513,9 +33513,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="8" t="inlineStr">
@@ -33568,9 +33568,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM14" s="6" t="inlineStr">
@@ -33810,14 +33810,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
@@ -33840,9 +33840,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="8" t="inlineStr">
@@ -33895,9 +33895,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM15" s="6" t="inlineStr">
@@ -34137,14 +34137,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="8" t="inlineStr">
@@ -34167,9 +34167,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="8" t="inlineStr">
@@ -34222,9 +34222,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM16" s="6" t="inlineStr">
@@ -34464,14 +34464,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
@@ -34494,9 +34494,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="8" t="inlineStr">
@@ -34549,9 +34549,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM17" s="6" t="inlineStr">
@@ -34791,14 +34791,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W18" s="8" t="inlineStr">
@@ -34821,9 +34821,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -34876,9 +34876,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -35118,14 +35118,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
@@ -35148,9 +35148,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="8" t="inlineStr">
@@ -35203,9 +35203,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -35445,14 +35445,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
@@ -35475,9 +35475,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="8" t="inlineStr">
@@ -35530,9 +35530,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -35772,14 +35772,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
@@ -35802,9 +35802,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="8" t="inlineStr">
@@ -35857,9 +35857,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -36184,9 +36184,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM22" s="8" t="inlineStr">
@@ -36511,9 +36511,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM23" s="8" t="inlineStr">
@@ -36838,9 +36838,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM24" s="8" t="inlineStr">
@@ -37819,9 +37819,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM27" s="8" t="inlineStr">
@@ -38146,9 +38146,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM28" s="8" t="inlineStr">
@@ -38473,9 +38473,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM29" s="8" t="inlineStr">
@@ -38800,9 +38800,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM30" s="8" t="inlineStr">
@@ -39127,9 +39127,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM31" s="8" t="inlineStr">
@@ -39454,9 +39454,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM32" s="8" t="inlineStr">
@@ -39781,9 +39781,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM33" s="8" t="inlineStr">
@@ -40108,9 +40108,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM34" s="8" t="inlineStr">
@@ -40350,14 +40350,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W35" s="8" t="inlineStr">
@@ -40380,9 +40380,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
@@ -40435,9 +40435,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM35" s="6" t="inlineStr">
@@ -40677,14 +40677,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W36" s="8" t="inlineStr">
@@ -40707,9 +40707,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB36" s="8" t="inlineStr">
@@ -40762,9 +40762,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM36" s="6" t="inlineStr">
@@ -41331,14 +41331,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W38" s="8" t="inlineStr">
@@ -41361,9 +41361,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB38" s="8" t="inlineStr">
@@ -41416,9 +41416,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM38" s="6" t="inlineStr">
@@ -41743,9 +41743,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM39" s="8" t="inlineStr">
@@ -41985,14 +41985,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W40" s="8" t="inlineStr">
@@ -42015,9 +42015,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB40" s="8" t="inlineStr">
@@ -42070,9 +42070,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM40" s="6" t="inlineStr">
@@ -42966,14 +42966,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W43" s="8" t="inlineStr">
@@ -42996,9 +42996,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB43" s="8" t="inlineStr">
@@ -43051,9 +43051,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM43" s="6" t="inlineStr">
@@ -43293,14 +43293,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W44" s="8" t="inlineStr">
@@ -43323,9 +43323,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB44" s="8" t="inlineStr">
@@ -43378,9 +43378,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM44" s="6" t="inlineStr">
@@ -43705,9 +43705,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM45" s="8" t="inlineStr">
@@ -45013,9 +45013,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM49" s="8" t="inlineStr">
@@ -48228,9 +48228,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA59" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB59" s="8" t="inlineStr">
@@ -48555,9 +48555,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA60" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB60" s="8" t="inlineStr">
@@ -48882,9 +48882,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB61" s="8" t="inlineStr">
@@ -49209,9 +49209,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA62" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB62" s="8" t="inlineStr">
@@ -49536,9 +49536,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA63" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA63" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB63" s="8" t="inlineStr">
@@ -49863,9 +49863,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB64" s="8" t="inlineStr">
@@ -50190,9 +50190,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB65" s="8" t="inlineStr">
@@ -50517,9 +50517,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA66" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB66" s="8" t="inlineStr">
@@ -50844,9 +50844,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB67" s="8" t="inlineStr">
@@ -51171,9 +51171,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB68" s="8" t="inlineStr">
@@ -51498,9 +51498,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA69" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB69" s="8" t="inlineStr">
@@ -51825,9 +51825,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA70" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB70" s="8" t="inlineStr">
@@ -51880,9 +51880,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM70" s="8" t="inlineStr">
@@ -52152,9 +52152,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB71" s="8" t="inlineStr">
@@ -52479,9 +52479,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB72" s="8" t="inlineStr">
@@ -52534,9 +52534,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM72" s="8" t="inlineStr">
@@ -52806,9 +52806,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA73" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB73" s="8" t="inlineStr">
@@ -53133,9 +53133,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB74" s="8" t="inlineStr">
@@ -53460,9 +53460,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA75" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB75" s="8" t="inlineStr">
@@ -53787,9 +53787,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB76" s="8" t="inlineStr">
@@ -54114,9 +54114,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA77" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB77" s="8" t="inlineStr">
@@ -54496,9 +54496,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM78" s="8" t="inlineStr">
@@ -54738,14 +54738,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W79" s="8" t="inlineStr">
@@ -54768,9 +54768,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB79" s="8" t="inlineStr">
@@ -54823,9 +54823,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM79" s="6" t="inlineStr">
@@ -55065,14 +55065,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W80" s="8" t="inlineStr">
@@ -55095,9 +55095,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB80" s="8" t="inlineStr">
@@ -55150,9 +55150,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL80" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL80" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM80" s="6" t="inlineStr">
@@ -55392,14 +55392,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W81" s="8" t="inlineStr">
@@ -55422,9 +55422,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB81" s="8" t="inlineStr">
@@ -55477,9 +55477,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM81" s="6" t="inlineStr">
@@ -55719,14 +55719,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W82" s="8" t="inlineStr">
@@ -55749,9 +55749,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB82" s="8" t="inlineStr">
@@ -55804,9 +55804,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM82" s="6" t="inlineStr">
@@ -56046,14 +56046,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W83" s="8" t="inlineStr">
@@ -56076,9 +56076,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB83" s="8" t="inlineStr">
@@ -56131,9 +56131,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM83" s="6" t="inlineStr">
@@ -56458,9 +56458,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM84" s="8" t="inlineStr">
@@ -56700,14 +56700,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W85" s="8" t="inlineStr">
@@ -56730,9 +56730,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB85" s="8" t="inlineStr">
@@ -56785,9 +56785,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM85" s="6" t="inlineStr">
@@ -57112,9 +57112,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM86" s="8" t="inlineStr">
@@ -57439,9 +57439,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM87" s="8" t="inlineStr">
@@ -57766,9 +57766,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL88" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM88" s="8" t="inlineStr">
@@ -58093,9 +58093,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL89" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM89" s="8" t="inlineStr">
@@ -58420,9 +58420,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM90" s="8" t="inlineStr">
@@ -59401,9 +59401,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL93" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM93" s="8" t="inlineStr">
@@ -59728,9 +59728,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL94" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM94" s="8" t="inlineStr">
@@ -60709,9 +60709,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL97" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM97" s="8" t="inlineStr">
@@ -61036,9 +61036,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL98" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL98" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM98" s="8" t="inlineStr">
@@ -61363,9 +61363,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL99" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL99" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM99" s="8" t="inlineStr">
@@ -62998,9 +62998,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL104" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL104" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM104" s="8" t="inlineStr">
@@ -63325,9 +63325,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL105" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL105" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM105" s="8" t="inlineStr">
@@ -63808,7 +63808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -63847,7 +63847,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -63857,14 +63857,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32F105VB</t>
+          <t>STM32F105VC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -63886,12 +63886,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32F107RB</t>
+          <t>STM32F105VB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -63901,14 +63901,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32F107RC</t>
+          <t>STM32F105VB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -63930,12 +63930,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32F107VB</t>
+          <t>STM32F107RB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -63945,14 +63945,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32F105R8</t>
+          <t>STM32F107RB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -63974,12 +63974,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32F105RB</t>
+          <t>STM32F107RC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -63989,14 +63989,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32F105RC</t>
+          <t>STM32F107RC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -64018,12 +64018,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F105V8</t>
+          <t>STM32F107VB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -64033,14 +64033,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F107VC</t>
+          <t>STM32F107VB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -64062,12 +64062,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32F103C4</t>
+          <t>STM32F105R8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -64077,19 +64077,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32F103R4</t>
+          <t>STM32F105R8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -64099,19 +64099,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F103C6</t>
+          <t>STM32F105RB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -64121,19 +64121,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F103R8</t>
+          <t>STM32F105RB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -64143,19 +64143,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F103RB</t>
+          <t>STM32F105RC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -64165,19 +64165,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32F103R6</t>
+          <t>STM32F105RC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -64187,19 +64187,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F103TB</t>
+          <t>STM32F105V8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -64209,19 +64209,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F103T4</t>
+          <t>STM32F105V8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -64231,19 +64231,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F103T8</t>
+          <t>STM32F107VC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -64253,19 +64253,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F103T6</t>
+          <t>STM32F107VC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -64275,14 +64275,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F103CB</t>
+          <t>STM32F103C4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -64297,14 +64297,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F103R4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -64319,14 +64319,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F103C6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -64341,14 +64341,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F103R8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -64363,14 +64363,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F103VB</t>
+          <t>STM32F103RB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -64385,14 +64385,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LFBGA100, LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F103R6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -64407,14 +64407,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F103TB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -64429,14 +64429,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists BGA144, LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F103ZG</t>
+          <t>STM32F103T4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -64451,14 +64451,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists BGA144, LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F103V8</t>
+          <t>STM32F103T8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -64473,14 +64473,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LFBGA100, LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F103C8</t>
+          <t>STM32F103T6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -64495,14 +64495,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx low-density device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F100VC</t>
+          <t>STM32F103CB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -64517,14 +64517,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F100CB</t>
+          <t>STM32F103RF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -64539,14 +64539,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F100VD</t>
+          <t>STM32F103RG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -64561,14 +64561,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F100R4</t>
+          <t>STM32F103VF</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -64583,14 +64583,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F100VE</t>
+          <t>STM32F103VB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -64605,14 +64605,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LFBGA100, LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F100R6</t>
+          <t>STM32F103VG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -64627,14 +64627,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F100R8</t>
+          <t>STM32F103ZF</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -64649,14 +64649,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists BGA144, LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F100RB</t>
+          <t>STM32F103ZG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -64671,14 +64671,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xF and STM32F103xG features and peripheral counts lists BGA144, LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F100RC</t>
+          <t>STM32F103V8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -64693,14 +64693,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LFBGA100, LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F100RD</t>
+          <t>STM32F103C8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -64715,14 +64715,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F103xx medium-density device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F100RE</t>
+          <t>STM32F100VC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -64737,14 +64737,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F100V8</t>
+          <t>STM32F100CB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -64759,14 +64759,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F100C4</t>
+          <t>STM32F100VD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -64781,14 +64781,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F100VB</t>
+          <t>STM32F100R4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -64803,14 +64803,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F100C6</t>
+          <t>STM32F100VE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -64825,14 +64825,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F100C8</t>
+          <t>STM32F100R6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -64847,14 +64847,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F100ZE</t>
+          <t>STM32F100R8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -64869,14 +64869,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F100ZC</t>
+          <t>STM32F100RB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -64891,14 +64891,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64, TFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F100ZD</t>
+          <t>STM32F100RC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -64913,14 +64913,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F101T4</t>
+          <t>STM32F100RD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -64935,14 +64935,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F101VG</t>
+          <t>STM32F100RE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -64957,14 +64957,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP100(1) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F101ZF</t>
+          <t>STM32F100V8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -64979,14 +64979,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F101ZG</t>
+          <t>STM32F100C4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -65001,14 +65001,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F101RF</t>
+          <t>STM32F100VB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -65023,14 +65023,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F101RG</t>
+          <t>STM32F100C6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -65045,14 +65045,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F101C4</t>
+          <t>STM32F100C8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -65067,14 +65067,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F101VF</t>
+          <t>STM32F100ZE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -65089,14 +65089,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP100(1) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F101C6</t>
+          <t>STM32F100ZC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -65111,14 +65111,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F101C8</t>
+          <t>STM32F100ZD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -65133,14 +65133,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F100xx features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F101R6</t>
+          <t>STM32F101T4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -65155,14 +65155,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F101R8</t>
+          <t>STM32F101VG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -65177,14 +65177,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP100(1) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F101TB</t>
+          <t>STM32F101ZF</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -65199,14 +65199,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 2. Device features and peripheral counts (STM32F101xx lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F101V8</t>
+          <t>STM32F101ZG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -65221,14 +65221,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F101VB</t>
+          <t>STM32F101RF</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -65243,14 +65243,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F101T8</t>
+          <t>STM32F101RG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -65265,14 +65265,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 2. Device features and peripheral counts (STM32F101xx lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F101T6</t>
+          <t>STM32F101C4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -65287,14 +65287,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F101R4</t>
+          <t>STM32F101VF</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -65309,14 +65309,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F101xF and STM32F101xG features and peripheral counts lists LQFP100(1) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F101CB</t>
+          <t>STM32F101C6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -65331,27 +65331,247 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists LQFP48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>STM32F101C8</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32F101R6</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32F101R8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32F101TB</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Table 2. Device features and peripheral counts (STM32F101xx lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32F101V8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32F101VB</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32F101T8</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 2. Device features and peripheral counts (STM32F101xx lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32F101T6</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists VFQFPN36 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32F101R4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 2. Low-density STM32F101xx device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32F101CB</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>STM32F101RB</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Table 2. Device features and peripheral counts (STM32F101xx lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>

--- a/product_selector_out/STM32F1 series.xlsx
+++ b/product_selector_out/STM32F1 series.xlsx
@@ -48288,9 +48288,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM59" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN59" s="8" t="inlineStr">
@@ -48942,9 +48942,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN61" s="8" t="inlineStr">
@@ -49596,9 +49596,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM63" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM63" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN63" s="8" t="inlineStr">
@@ -50904,9 +50904,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN67" s="8" t="inlineStr">
@@ -51231,9 +51231,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN68" s="8" t="inlineStr">
@@ -51558,9 +51558,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM69" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN69" s="8" t="inlineStr">
@@ -53520,9 +53520,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM75" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN75" s="8" t="inlineStr">
@@ -53847,9 +53847,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN76" s="8" t="inlineStr">
@@ -54174,9 +54174,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM77" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN77" s="8" t="inlineStr">

--- a/product_selector_out/STM32F1 series.xlsx
+++ b/product_selector_out/STM32F1 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM106"/>
+  <dimension ref="A1:BN106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.52734375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c4.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c4.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c4.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c8.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c8.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c4.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c8.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c4.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c8.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c4.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c8.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rf.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rf.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rf.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c8.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rf.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rf.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rf.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c8.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103c8.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f103rc.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c8.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c4.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c4.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c8.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c8.pdf</t>
         </is>
       </c>
@@ -15702,6 +15929,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c4.pdf</t>
         </is>
       </c>
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c4.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c8.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -18645,6 +18917,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -18972,6 +19249,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -19299,6 +19581,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -19626,6 +19913,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -19953,6 +20245,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -20280,6 +20577,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -20607,6 +20909,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -20934,6 +21241,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -21261,6 +21573,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -21588,6 +21905,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100c4.pdf</t>
         </is>
       </c>
@@ -21915,6 +22237,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -22242,6 +22569,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -22569,6 +22901,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f100rc.pdf</t>
         </is>
       </c>
@@ -22896,6 +23233,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -23223,6 +23565,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -23550,6 +23897,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -23877,6 +24229,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -24204,6 +24561,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -24531,6 +24893,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -24858,6 +25225,11 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -25185,6 +25557,11 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -25512,6 +25889,11 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -25839,6 +26221,11 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -26166,6 +26553,11 @@
       </c>
       <c r="BM88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -26493,6 +26885,11 @@
       </c>
       <c r="BM89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -26820,6 +27217,11 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -27147,6 +27549,11 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -27474,6 +27881,11 @@
       </c>
       <c r="BM92" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN92" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -27801,6 +28213,11 @@
       </c>
       <c r="BM93" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -28128,6 +28545,11 @@
       </c>
       <c r="BM94" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -28455,6 +28877,11 @@
       </c>
       <c r="BM95" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN95" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -28782,6 +29209,11 @@
       </c>
       <c r="BM96" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN96" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -29109,6 +29541,11 @@
       </c>
       <c r="BM97" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN97" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -29436,6 +29873,11 @@
       </c>
       <c r="BM98" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN98" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -29763,6 +30205,11 @@
       </c>
       <c r="BM99" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN99" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -30090,6 +30537,11 @@
       </c>
       <c r="BM100" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN100" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -30417,6 +30869,11 @@
       </c>
       <c r="BM101" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN101" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -30744,6 +31201,11 @@
       </c>
       <c r="BM102" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN102" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -31071,6 +31533,11 @@
       </c>
       <c r="BM103" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN103" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -31398,6 +31865,11 @@
       </c>
       <c r="BM104" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN104" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -31725,6 +32197,11 @@
       </c>
       <c r="BM105" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN105" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -32052,12 +32529,17 @@
       </c>
       <c r="BM106" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN106" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -32078,16 +32560,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -32100,6 +32580,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -32119,7 +32600,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -32231,7 +32714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM106"/>
+  <dimension ref="A1:BN106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -32299,6 +32782,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32632,6 +33116,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -32727,6 +33216,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -33049,7 +33539,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33376,7 +33871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33703,7 +34203,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34030,7 +34535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34357,7 +34867,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34684,7 +35199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35011,7 +35531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35338,7 +35863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35665,7 +36195,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35992,7 +36527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36319,7 +36859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36646,7 +37191,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36973,7 +37523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37300,7 +37855,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37627,7 +38187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37954,7 +38519,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38281,7 +38851,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38608,7 +39183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38935,7 +39515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39262,7 +39847,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39589,7 +40179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39916,7 +40511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40243,7 +40843,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40570,7 +41175,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40897,7 +41507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41224,7 +41839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41551,7 +42171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41878,7 +42503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42205,7 +42835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42532,7 +43167,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42859,7 +43499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43186,7 +43831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43513,7 +44163,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43840,7 +44495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44167,7 +44827,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44494,7 +45159,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44821,7 +45491,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45148,7 +45823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45475,7 +46155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45802,7 +46487,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46129,7 +46819,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46456,7 +47151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46783,7 +47483,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47110,7 +47815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47437,7 +48147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47764,7 +48479,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48091,7 +48811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48418,7 +49143,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48745,7 +49475,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49072,7 +49807,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49399,7 +50139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49726,7 +50471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50053,7 +50803,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50380,7 +51135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50707,7 +51467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51034,7 +51799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51361,7 +52131,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51688,7 +52463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52015,7 +52795,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52342,7 +53127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52669,7 +53459,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52996,7 +53791,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53323,7 +54123,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53650,7 +54455,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53977,7 +54787,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54304,7 +55119,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54631,7 +55451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54958,7 +55783,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55285,7 +56115,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55612,7 +56447,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55939,7 +56779,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56266,7 +57111,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56593,7 +57443,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56920,7 +57775,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57247,7 +58107,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57574,7 +58439,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57901,7 +58771,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM88" s="6" t="inlineStr">
+      <c r="BM88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58228,7 +59103,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM89" s="6" t="inlineStr">
+      <c r="BM89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58555,7 +59435,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
+      <c r="BM90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58882,7 +59767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM91" s="6" t="inlineStr">
+      <c r="BM91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59209,7 +60099,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM92" s="6" t="inlineStr">
+      <c r="BM92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN92" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59536,7 +60431,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM93" s="6" t="inlineStr">
+      <c r="BM93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59863,7 +60763,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM94" s="6" t="inlineStr">
+      <c r="BM94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60190,7 +61095,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM95" s="6" t="inlineStr">
+      <c r="BM95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN95" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60517,7 +61427,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM96" s="6" t="inlineStr">
+      <c r="BM96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN96" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60844,7 +61759,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM97" s="6" t="inlineStr">
+      <c r="BM97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN97" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61171,7 +62091,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM98" s="6" t="inlineStr">
+      <c r="BM98" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN98" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61498,7 +62423,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM99" s="6" t="inlineStr">
+      <c r="BM99" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN99" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61825,7 +62755,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM100" s="6" t="inlineStr">
+      <c r="BM100" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN100" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62152,7 +63087,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM101" s="6" t="inlineStr">
+      <c r="BM101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN101" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62479,7 +63419,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM102" s="6" t="inlineStr">
+      <c r="BM102" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN102" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62806,7 +63751,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM103" s="6" t="inlineStr">
+      <c r="BM103" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN103" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63133,7 +64083,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM104" s="6" t="inlineStr">
+      <c r="BM104" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN104" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63460,7 +64415,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM105" s="6" t="inlineStr">
+      <c r="BM105" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN105" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63787,7 +64747,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM106" s="6" t="inlineStr">
+      <c r="BM106" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN106" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63795,8 +64760,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
